--- a/Plannings 2026 S34.xlsx
+++ b/Plannings 2026 S34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5845C06-B34D-4CFD-B82C-4A1429626F94}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="83">
   <si>
     <t>Planning des salariés du 17/08/2026 au 23/08/2026</t>
   </si>
@@ -179,9 +179,6 @@
   </si>
   <si>
     <t>DOVINA Théo</t>
-  </si>
-  <si>
-    <t>20:00/24:00</t>
   </si>
   <si>
     <t>19:00/24:00</t>
@@ -2996,50 +2993,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="123825" cy="123825"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
@@ -4672,7 +4625,7 @@
     </row>
     <row r="3" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="44" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
@@ -4950,7 +4903,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5229,9 +5182,7 @@
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="18" t="s">
-        <v>12</v>
-      </c>
+      <c r="D35" s="18"/>
       <c r="E35" s="18" t="s">
         <v>12</v>
       </c>
@@ -5245,11 +5196,9 @@
       <c r="A36" s="20"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="22" t="s">
+      <c r="D36" s="22"/>
+      <c r="E36" s="22" t="s">
         <v>48</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>49</v>
       </c>
       <c r="F36" s="22" t="s">
         <v>44</v>
@@ -5259,7 +5208,7 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
@@ -5271,7 +5220,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="26"/>
@@ -5283,7 +5232,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" s="31"/>
       <c r="C39" s="32"/>
@@ -5295,7 +5244,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B40" s="37" t="s">
         <v>17</v>
@@ -5398,19 +5347,19 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="28"/>
       <c r="B45" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="29"/>
@@ -5517,7 +5466,7 @@
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="26"/>
@@ -5529,7 +5478,7 @@
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="26"/>
@@ -5541,7 +5490,7 @@
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="26"/>
@@ -5553,7 +5502,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -5574,12 +5523,12 @@
       <c r="F56" s="22"/>
       <c r="G56" s="22"/>
       <c r="H56" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="26"/>
@@ -5591,7 +5540,7 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="26"/>
@@ -5603,10 +5552,10 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
@@ -5617,7 +5566,7 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="26"/>
@@ -5629,7 +5578,7 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -5641,7 +5590,7 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="26"/>
@@ -5653,7 +5602,7 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -5722,7 +5671,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -5730,7 +5679,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -5741,16 +5690,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5925,7 +5874,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -5942,7 +5891,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -5959,7 +5908,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -5976,7 +5925,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -5993,7 +5942,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -6010,7 +5959,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -6027,7 +5976,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -6044,7 +5993,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -6061,7 +6010,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -6078,7 +6027,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -6095,7 +6044,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -6112,7 +6061,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -6129,7 +6078,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -6146,7 +6095,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -6163,7 +6112,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -6180,7 +6129,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -6230,40 +6179,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -6444,13 +6393,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5C027A0-44BD-4A75-841B-07F4C346E0F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2E62D-B5C2-4797-8435-153EB3ADEDA3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67EC5373-55CE-4190-A766-361458A103D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776D5F97-2FA8-4677-BB70-78096B3628DE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BC4490-B2FC-4F13-B0AE-74C335B88878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF84BC3-7FCF-4F2C-B2F1-F8A377E9AC78}"/>
 </file>
--- a/Plannings 2026 S34.xlsx
+++ b/Plannings 2026 S34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5845C06-B34D-4CFD-B82C-4A1429626F94}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="84">
   <si>
     <t>Planning des salariés du 17/08/2026 au 23/08/2026</t>
   </si>
@@ -179,6 +179,9 @@
   </si>
   <si>
     <t>DOVINA Théo</t>
+  </si>
+  <si>
+    <t>20:00/24:00</t>
   </si>
   <si>
     <t>19:00/24:00</t>
@@ -2993,6 +2996,50 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="51" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>34</xdr:row>
@@ -4625,7 +4672,7 @@
     </row>
     <row r="3" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
@@ -4903,7 +4950,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5182,7 +5229,9 @@
       </c>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
+      <c r="D35" s="18" t="s">
+        <v>12</v>
+      </c>
       <c r="E35" s="18" t="s">
         <v>12</v>
       </c>
@@ -5196,9 +5245,11 @@
       <c r="A36" s="20"/>
       <c r="B36" s="22"/>
       <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
+      <c r="D36" s="22" t="s">
+        <v>48</v>
+      </c>
       <c r="E36" s="22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F36" s="22" t="s">
         <v>44</v>
@@ -5208,7 +5259,7 @@
     </row>
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
@@ -5220,7 +5271,7 @@
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="26"/>
@@ -5232,7 +5283,7 @@
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39" s="31"/>
       <c r="C39" s="32"/>
@@ -5244,7 +5295,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40" s="37" t="s">
         <v>17</v>
@@ -5347,19 +5398,19 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="28"/>
       <c r="B45" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C45" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="29"/>
@@ -5466,7 +5517,7 @@
     </row>
     <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="26"/>
@@ -5478,7 +5529,7 @@
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="26"/>
@@ -5490,7 +5541,7 @@
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="26"/>
@@ -5502,7 +5553,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
@@ -5523,12 +5574,12 @@
       <c r="F56" s="22"/>
       <c r="G56" s="22"/>
       <c r="H56" s="23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="26"/>
@@ -5540,7 +5591,7 @@
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="26"/>
@@ -5552,10 +5603,10 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
@@ -5566,7 +5617,7 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="26"/>
@@ -5578,7 +5629,7 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -5590,7 +5641,7 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="26"/>
@@ -5602,7 +5653,7 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -5671,7 +5722,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -5679,7 +5730,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -5690,16 +5741,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5874,7 +5925,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -5891,7 +5942,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -5908,7 +5959,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -5925,7 +5976,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -5942,7 +5993,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -5959,7 +6010,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -5976,7 +6027,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -5993,7 +6044,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -6010,7 +6061,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -6027,7 +6078,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -6044,7 +6095,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -6061,7 +6112,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -6078,7 +6129,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -6095,7 +6146,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -6112,7 +6163,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -6129,7 +6180,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -6179,40 +6230,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -6393,13 +6444,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2E62D-B5C2-4797-8435-153EB3ADEDA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5C027A0-44BD-4A75-841B-07F4C346E0F4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776D5F97-2FA8-4677-BB70-78096B3628DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67EC5373-55CE-4190-A766-361458A103D5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF84BC3-7FCF-4F2C-B2F1-F8A377E9AC78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BC4490-B2FC-4F13-B0AE-74C335B88878}"/>
 </file>
--- a/Plannings 2026 S34.xlsx
+++ b/Plannings 2026 S34.xlsx
@@ -6393,13 +6393,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1C2E62D-B5C2-4797-8435-153EB3ADEDA3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A4DDE7B-1EE1-49B8-8BC4-2D0A537C2D02}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{776D5F97-2FA8-4677-BB70-78096B3628DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EFB1F1-CC44-4B80-9103-37727524A62C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF84BC3-7FCF-4F2C-B2F1-F8A377E9AC78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370F5A98-EEF1-4513-A2BD-EAC7AF790B16}"/>
 </file>
--- a/Plannings 2026 S34.xlsx
+++ b/Plannings 2026 S34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5845C06-B34D-4CFD-B82C-4A1429626F94}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02A0EF9B-B3FE-4C6A-835D-C1C1F9D6F731}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -679,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,6 +811,9 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,13 +842,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -883,13 +886,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -927,13 +930,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -971,13 +974,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1015,13 +1018,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1059,13 +1062,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1103,13 +1106,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1147,13 +1150,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1191,13 +1194,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1235,13 +1238,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1279,13 +1282,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1323,13 +1326,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1367,13 +1370,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1411,13 +1414,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1455,13 +1458,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1499,13 +1502,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1543,13 +1546,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1587,13 +1590,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1631,13 +1634,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1675,13 +1678,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1719,13 +1722,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1763,13 +1766,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1807,13 +1810,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1851,13 +1854,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1895,13 +1898,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1939,13 +1942,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1983,13 +1986,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2027,13 +2030,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2071,13 +2074,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2115,13 +2118,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2159,13 +2162,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2203,13 +2206,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2247,13 +2250,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2291,13 +2294,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2335,13 +2338,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2379,13 +2382,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2423,13 +2426,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2467,13 +2470,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2511,13 +2514,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2555,13 +2558,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2599,13 +2602,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2643,13 +2646,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2687,13 +2690,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2731,13 +2734,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2775,13 +2778,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2819,13 +2822,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2863,13 +2866,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2907,13 +2910,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2951,13 +2954,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2995,13 +2998,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3039,13 +3042,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>35</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3083,13 +3086,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3127,13 +3130,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3171,13 +3174,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3215,13 +3218,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3259,13 +3262,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3303,13 +3306,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3347,13 +3350,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3391,13 +3394,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3435,13 +3438,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3479,13 +3482,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3523,13 +3526,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3567,13 +3570,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3611,13 +3614,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3655,13 +3658,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3699,13 +3702,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3743,13 +3746,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3787,13 +3790,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3831,13 +3834,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3875,13 +3878,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3919,13 +3922,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3963,13 +3966,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4007,13 +4010,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4051,13 +4054,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4095,13 +4098,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4139,13 +4142,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4183,13 +4186,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -4595,7 +4598,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="34" customWidth="1"/>
@@ -4634,221 +4637,214 @@
       <c r="G3" s="44"/>
       <c r="H3" s="44"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H5" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H6" s="19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22" t="s">
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H7" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="27"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="27"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B9" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G9" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="29"/>
+      <c r="H9" s="19"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="29"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="29"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
-      <c r="B11" s="22" t="s">
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="29"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="20"/>
+      <c r="B12" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="23"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="27"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F14" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="18"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="29"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="28"/>
       <c r="B15" s="1"/>
-      <c r="C15" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="G15" s="1"/>
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="28"/>
       <c r="B16" s="1"/>
-      <c r="C16" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>28</v>
+      <c r="C16" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>27</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -4857,370 +4853,374 @@
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="28"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
+      <c r="C17" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>28</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="29"/>
     </row>
-    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="28"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D19" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E19" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="27"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="B20" s="25"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="27"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B21" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="37" t="s">
+      <c r="D22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="E22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="37" t="s">
+      <c r="F22" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="29"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="28"/>
-      <c r="B23" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>37</v>
+      <c r="B23" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>36</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="29"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="28"/>
-      <c r="B24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="38" t="s">
-        <v>38</v>
+      <c r="B24" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="29"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="28"/>
-      <c r="B25" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>17</v>
+      <c r="B25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="29"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="28"/>
-      <c r="B26" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>28</v>
+      <c r="B26" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="29"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
-      <c r="B27" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>37</v>
+      <c r="B27" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>28</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="29"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="28"/>
-      <c r="B28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>39</v>
+      <c r="B28" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="29"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
-      <c r="B29" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="38"/>
-      <c r="D29" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="38"/>
-      <c r="F29" s="39" t="s">
-        <v>17</v>
+      <c r="B29" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>39</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="29"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
-      <c r="B30" s="38" t="s">
-        <v>40</v>
+      <c r="B30" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="C30" s="38"/>
-      <c r="D30" s="38" t="s">
-        <v>40</v>
+      <c r="D30" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="E30" s="38"/>
-      <c r="F30" s="38" t="s">
-        <v>40</v>
+      <c r="F30" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="29"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
-      <c r="B31" s="39" t="s">
-        <v>37</v>
+      <c r="B31" s="38" t="s">
+        <v>40</v>
       </c>
       <c r="C31" s="38"/>
-      <c r="D31" s="39" t="s">
-        <v>37</v>
+      <c r="D31" s="38" t="s">
+        <v>40</v>
       </c>
       <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
+      <c r="F31" s="38" t="s">
+        <v>40</v>
+      </c>
       <c r="G31" s="1"/>
       <c r="H31" s="29"/>
     </row>
-    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20"/>
-      <c r="B32" s="40" t="s">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="28"/>
+      <c r="B32" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="38"/>
+      <c r="D32" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40" t="s">
+      <c r="C33" s="40"/>
+      <c r="D33" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="23"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="23"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B34" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C34" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D34" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E34" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="19" t="s">
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="20"/>
-      <c r="B34" s="22" t="s">
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="20"/>
+      <c r="B35" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C35" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D35" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="22" t="s">
+      <c r="E35" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="23" t="s">
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18" t="s">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F36" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="20"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22" t="s">
+      <c r="G36" s="18"/>
+      <c r="H36" s="19"/>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="20"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="22" t="s">
+      <c r="F37" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="G36" s="22"/>
-      <c r="H36" s="23"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="27"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="23"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="26"/>
@@ -5231,191 +5231,187 @@
       <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="27"/>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="33"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="B40" s="31"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="33"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="B40" s="37" t="s">
+      <c r="B41" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C41" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D41" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="E40" s="37" t="s">
+      <c r="E41" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F41" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="G40" s="18"/>
-      <c r="H40" s="19"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
-      <c r="B41" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="E41" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="29"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="19"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="28"/>
-      <c r="B42" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E42" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="39" t="s">
-        <v>37</v>
+      <c r="B42" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D42" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>35</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="29"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="28"/>
-      <c r="B43" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>38</v>
+      <c r="B43" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="29"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="28"/>
-      <c r="B44" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>17</v>
+      <c r="B44" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D44" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="29"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="28"/>
-      <c r="B45" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>54</v>
+      <c r="B45" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="29"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="28"/>
-      <c r="B46" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="E46" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F46" s="39" t="s">
-        <v>37</v>
+      <c r="B46" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>54</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="29"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="28"/>
-      <c r="B47" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D47" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="F47" s="38" t="s">
-        <v>39</v>
+      <c r="B47" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="29"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="28"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="38"/>
-      <c r="E48" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>17</v>
+      <c r="B48" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>39</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="29"/>
@@ -5423,15 +5419,15 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="28"/>
       <c r="B49" s="38"/>
-      <c r="C49" s="38" t="s">
-        <v>40</v>
+      <c r="C49" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="D49" s="38"/>
-      <c r="E49" s="38" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" s="38" t="s">
-        <v>40</v>
+      <c r="E49" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="F49" s="39" t="s">
+        <v>17</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="29"/>
@@ -5439,46 +5435,50 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="28"/>
       <c r="B50" s="38"/>
-      <c r="C50" s="39" t="s">
-        <v>37</v>
+      <c r="C50" s="38" t="s">
+        <v>40</v>
       </c>
       <c r="D50" s="38"/>
-      <c r="E50" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="F50" s="38"/>
+      <c r="E50" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>40</v>
+      </c>
       <c r="G50" s="1"/>
       <c r="H50" s="29"/>
     </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="20"/>
-      <c r="B51" s="40"/>
-      <c r="C51" s="40" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="28"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" s="38"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="29"/>
+    </row>
+    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="40"/>
+      <c r="C52" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40" t="s">
+      <c r="D52" s="40"/>
+      <c r="E52" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F51" s="40"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="23"/>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="25"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="27"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="23"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="26"/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="26"/>
@@ -5500,47 +5500,47 @@
       <c r="G54" s="26"/>
       <c r="H54" s="27"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
+    <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="25"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="27"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
-      <c r="H55" s="19" t="s">
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="20"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="23" t="s">
+    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="20"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="23" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="B57" s="25"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="26"/>
@@ -5552,11 +5552,9 @@
     </row>
     <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="B59" s="25" t="s">
-        <v>81</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="B59" s="25"/>
       <c r="C59" s="26"/>
       <c r="D59" s="26"/>
       <c r="E59" s="26"/>
@@ -5566,9 +5564,11 @@
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="B60" s="25"/>
+        <v>62</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>81</v>
+      </c>
       <c r="C60" s="26"/>
       <c r="D60" s="26"/>
       <c r="E60" s="26"/>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="26"/>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -5612,45 +5612,57 @@
       <c r="G63" s="26"/>
       <c r="H63" s="27"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="36"/>
-      <c r="E64" s="36"/>
-      <c r="F64" s="36"/>
-      <c r="G64" s="36"/>
-      <c r="H64" s="36"/>
+    <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="25"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="27"/>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="36"/>
+      <c r="C65" s="36"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="36"/>
+      <c r="G65" s="36"/>
+      <c r="H65" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B54:H54"/>
     <mergeCell ref="B60:H60"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B57:H57"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B53:H53"/>
-    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B40:H40"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B64:H64"/>
-    <mergeCell ref="B61:H61"/>
+    <mergeCell ref="B53:H53"/>
+    <mergeCell ref="B65:H65"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="B63:H63"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A40:A51"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A13:A18"/>
-    <mergeCell ref="A21:A32"/>
+    <mergeCell ref="B64:H64"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A41:A52"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A22:A33"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A9:A12"/>
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6393,13 +6405,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A4DDE7B-1EE1-49B8-8BC4-2D0A537C2D02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFA44321-39B8-46A0-A313-7752430BF8FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7EFB1F1-CC44-4B80-9103-37727524A62C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C7CBE71-3C8A-4919-A5A1-4EC5F398E9C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370F5A98-EEF1-4513-A2BD-EAC7AF790B16}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F4041EC-0CEA-451E-870B-3E0A14B11723}"/>
 </file>
--- a/Plannings 2026 S34.xlsx
+++ b/Plannings 2026 S34.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E93FD0BA-AF21-460D-A633-AD05E69F6585}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{559C6429-F12D-441A-BD84-FBDC171A605E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7572AFE8-2A28-4681-A10D-FE1410D387FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="87">
   <si>
     <t>Planning des salariés du 17/08/2026 au 23/08/2026</t>
   </si>
@@ -103,9 +103,6 @@
     <t>08:45/15:00</t>
   </si>
   <si>
-    <t>09:45/17:00</t>
-  </si>
-  <si>
     <t>CASTELLON Pascaline</t>
   </si>
   <si>
@@ -286,10 +283,19 @@
     <t>Commercial : Summer Cp</t>
   </si>
   <si>
-    <t>P25</t>
-  </si>
-  <si>
-    <t>P100</t>
+    <t>CUP-L</t>
+  </si>
+  <si>
+    <t>07:30/08:45</t>
+  </si>
+  <si>
+    <t>09:45/16:30</t>
+  </si>
+  <si>
+    <t>P25 // STAGE</t>
+  </si>
+  <si>
+    <t>STAGE // P100</t>
   </si>
 </sst>
 </file>
@@ -4232,6 +4238,226 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="81" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBA42C74-1FD2-43AB-B52F-50CE2220F375}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2486025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="82" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F30607C-9AB6-435D-B9CE-43E7B66545A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="2867025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="83" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DD93297-7F58-4468-BA38-DDF5C21A77B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609600" y="3248025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="84" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A4FE7D9-45C6-47C8-8F9B-D49D6296D16D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1219200" y="2486025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="85" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A962EAA2-C5B7-4752-90B2-7985D70DA601}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1828800" y="2486025"/>
+          <a:ext cx="123825" cy="123825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4607,7 +4833,7 @@
   <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="34" customWidth="1"/>
+    <col min="1" max="8" width="36.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4634,7 +4860,7 @@
     </row>
     <row r="3" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="44" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="44"/>
@@ -4645,13 +4871,19 @@
     </row>
     <row r="4" spans="1:8" s="43" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
+        <v>85</v>
+      </c>
+      <c r="C4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>17</v>
+      </c>
       <c r="F4" s="45" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G4" s="45"/>
       <c r="H4" s="45"/>
@@ -4728,13 +4960,13 @@
       <c r="A9" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="37" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="18" t="s">
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E9" s="18" t="s">
@@ -4750,14 +4982,14 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="28"/>
-      <c r="B10" s="38" t="s">
-        <v>18</v>
+      <c r="B10" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>20</v>
@@ -4772,7 +5004,9 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="28"/>
-      <c r="B11" s="38"/>
+      <c r="B11" s="39" t="s">
+        <v>17</v>
+      </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -4782,7 +5016,9 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="28"/>
-      <c r="B12" s="38"/>
+      <c r="B12" s="38" t="s">
+        <v>18</v>
+      </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -4804,11 +5040,11 @@
     </row>
     <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20"/>
-      <c r="B14" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
+      <c r="B14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="22"/>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
@@ -4816,7 +5052,7 @@
     </row>
     <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="26"/>
@@ -4828,7 +5064,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18" t="s">
@@ -4850,16 +5086,16 @@
       <c r="A17" s="28"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="29"/>
@@ -4868,13 +5104,13 @@
       <c r="A18" s="28"/>
       <c r="B18" s="1"/>
       <c r="C18" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -4884,13 +5120,13 @@
       <c r="A19" s="28"/>
       <c r="B19" s="1"/>
       <c r="C19" s="42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -4916,13 +5152,13 @@
       <c r="A21" s="20"/>
       <c r="B21" s="22"/>
       <c r="C21" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>30</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>31</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -4930,7 +5166,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="26"/>
@@ -4942,10 +5178,10 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -4956,7 +5192,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="37" t="s">
         <v>17</v>
@@ -4979,19 +5215,19 @@
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="28"/>
       <c r="B25" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="E25" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="38" t="s">
         <v>35</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="F25" s="38" t="s">
-        <v>36</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="29"/>
@@ -4999,19 +5235,19 @@
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="28"/>
       <c r="B26" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="29"/>
@@ -5019,19 +5255,19 @@
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="28"/>
       <c r="B27" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="29"/>
@@ -5059,19 +5295,19 @@
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="28"/>
       <c r="B29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="29"/>
@@ -5079,19 +5315,19 @@
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="28"/>
       <c r="B30" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="29"/>
@@ -5099,19 +5335,19 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="28"/>
       <c r="B31" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D31" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="29"/>
@@ -5135,15 +5371,15 @@
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="28"/>
       <c r="B33" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33" s="38"/>
       <c r="D33" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" s="38"/>
       <c r="F33" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="29"/>
@@ -5151,11 +5387,11 @@
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="28"/>
       <c r="B34" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C34" s="38"/>
       <c r="D34" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E34" s="38"/>
       <c r="F34" s="38"/>
@@ -5165,11 +5401,11 @@
     <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20"/>
       <c r="B35" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" s="40"/>
       <c r="D35" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35" s="40"/>
       <c r="F35" s="40"/>
@@ -5178,7 +5414,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>12</v>
@@ -5201,26 +5437,26 @@
     <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20"/>
       <c r="B37" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="D37" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>44</v>
-      </c>
-      <c r="D37" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>45</v>
       </c>
       <c r="F37" s="35"/>
       <c r="G37" s="35"/>
       <c r="H37" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="18"/>
       <c r="C38" s="18"/>
@@ -5240,17 +5476,17 @@
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
       <c r="E39" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G39" s="22"/>
       <c r="H39" s="23"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="26"/>
@@ -5262,7 +5498,7 @@
     </row>
     <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="26"/>
@@ -5274,7 +5510,7 @@
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" s="31"/>
       <c r="C42" s="32"/>
@@ -5286,7 +5522,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="37" t="s">
         <v>17</v>
@@ -5309,19 +5545,19 @@
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="28"/>
       <c r="B44" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C44" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C44" s="38" t="s">
-        <v>36</v>
-      </c>
       <c r="D44" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="E44" s="38" t="s">
-        <v>36</v>
-      </c>
       <c r="F44" s="38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="29"/>
@@ -5329,19 +5565,19 @@
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="28"/>
       <c r="B45" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E45" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F45" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="29"/>
@@ -5349,19 +5585,19 @@
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="28"/>
       <c r="B46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="29"/>
@@ -5389,19 +5625,19 @@
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="28"/>
       <c r="B48" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="29"/>
@@ -5409,19 +5645,19 @@
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="28"/>
       <c r="B49" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C49" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D49" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E49" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F49" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="29"/>
@@ -5429,19 +5665,19 @@
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="28"/>
       <c r="B50" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F50" s="38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="29"/>
@@ -5466,14 +5702,14 @@
       <c r="A52" s="28"/>
       <c r="B52" s="38"/>
       <c r="C52" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D52" s="38"/>
       <c r="E52" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F52" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="29"/>
@@ -5482,11 +5718,11 @@
       <c r="A53" s="28"/>
       <c r="B53" s="38"/>
       <c r="C53" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D53" s="38"/>
       <c r="E53" s="39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F53" s="38"/>
       <c r="G53" s="1"/>
@@ -5496,11 +5732,11 @@
       <c r="A54" s="20"/>
       <c r="B54" s="40"/>
       <c r="C54" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D54" s="40"/>
       <c r="E54" s="40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F54" s="40"/>
       <c r="G54" s="22"/>
@@ -5508,7 +5744,7 @@
     </row>
     <row r="55" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="26"/>
@@ -5520,7 +5756,7 @@
     </row>
     <row r="56" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="26"/>
@@ -5532,7 +5768,7 @@
     </row>
     <row r="57" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="26"/>
@@ -5544,7 +5780,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
@@ -5565,12 +5801,12 @@
       <c r="F59" s="22"/>
       <c r="G59" s="22"/>
       <c r="H59" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="26"/>
@@ -5582,7 +5818,7 @@
     </row>
     <row r="61" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -5594,10 +5830,10 @@
     </row>
     <row r="62" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C62" s="26"/>
       <c r="D62" s="26"/>
@@ -5608,7 +5844,7 @@
     </row>
     <row r="63" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -5620,7 +5856,7 @@
     </row>
     <row r="64" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="26"/>
@@ -5632,7 +5868,7 @@
     </row>
     <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="26"/>
@@ -5644,7 +5880,7 @@
     </row>
     <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="26"/>
@@ -5696,7 +5932,7 @@
     <mergeCell ref="B3:H3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -5713,7 +5949,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B4" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -5721,7 +5957,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B5" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -5732,16 +5968,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5797,7 +6033,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="7">
         <v>0</v>
@@ -5814,7 +6050,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
         <v>0</v>
@@ -5831,7 +6067,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="7">
         <v>0</v>
@@ -5848,7 +6084,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="7">
         <v>0</v>
@@ -5865,7 +6101,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7">
         <v>0</v>
@@ -5882,7 +6118,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="7">
         <v>0</v>
@@ -5899,7 +6135,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="7">
         <v>0</v>
@@ -5916,7 +6152,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="7">
         <v>0</v>
@@ -5933,7 +6169,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="7">
         <v>0</v>
@@ -5950,7 +6186,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="7">
         <v>0</v>
@@ -5967,7 +6203,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" s="7">
         <v>0</v>
@@ -5984,7 +6220,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="7">
         <v>0</v>
@@ -6001,7 +6237,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22" s="7">
         <v>0</v>
@@ -6018,7 +6254,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="7">
         <v>0</v>
@@ -6035,7 +6271,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24" s="7">
         <v>0</v>
@@ -6052,7 +6288,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25" s="7">
         <v>0</v>
@@ -6069,7 +6305,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B26" s="7">
         <v>0</v>
@@ -6086,7 +6322,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" s="7">
         <v>0</v>
@@ -6103,7 +6339,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B28" s="7">
         <v>0</v>
@@ -6120,7 +6356,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B29" s="7">
         <v>0</v>
@@ -6137,7 +6373,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" s="7">
         <v>0</v>
@@ -6154,7 +6390,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B31" s="7">
         <v>0</v>
@@ -6171,7 +6407,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" s="7">
         <v>0</v>
@@ -6221,40 +6457,40 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="11"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>77</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -6435,13 +6671,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF4A0283-FC6E-41B1-8E35-D6CF879D810B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93742B51-B32D-45F5-A3C2-28A553C3C2FE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E433227-841E-46E2-BAA4-3FC7C4FE501C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C85A56B2-D034-4343-A5AA-6DB8F974E5AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3850CFE-A224-4DB9-90C9-4159BF0E15E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44903281-4A62-437F-8C92-0C692F4CB83C}"/>
 </file>